--- a/HUMAN_VERIFICATION_25_PARTS.xlsx
+++ b/HUMAN_VERIFICATION_25_PARTS.xlsx
@@ -451,22 +451,22 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C2" t="str">
-        <v>norm_case_1789766302590_46</v>
+        <v>norm_case_1789766302590_94</v>
       </c>
       <c r="D2" t="str">
-        <v>FREE ROLLER</v>
+        <v>MOTOR SHAFT</v>
       </c>
       <c r="E2" t="str">
-        <v>SS400</v>
+        <v>S45C</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3.994</v>
+        <v>31.961</v>
       </c>
       <c r="H2" t="str">
-        <v>424×400×3</v>
+        <v>360×226.6×0</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -483,10 +483,10 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C3" t="str">
-        <v>norm_case_1789766302590_60</v>
+        <v>norm_case_1789766302590_94</v>
       </c>
       <c r="D3" t="str">
-        <v>SPACER COLLAR</v>
+        <v>MOTOR SHAFT</v>
       </c>
       <c r="E3" t="str">
         <v>S45C</v>
@@ -495,10 +495,10 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>3.468</v>
+        <v>29.076</v>
       </c>
       <c r="H3" t="str">
-        <v>460.1×320.1×3</v>
+        <v>327.5×226.6×0</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -515,22 +515,22 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C4" t="str">
-        <v>norm_case_1789766302590_61</v>
+        <v>norm_case_1789766302590_81</v>
       </c>
       <c r="D4" t="str">
-        <v>HINGE SHAFT</v>
+        <v>PIN TYPE GATE CONVEYOR</v>
       </c>
       <c r="E4" t="str">
-        <v>S45C</v>
+        <v>AL6061</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3.468</v>
+        <v>10.52</v>
       </c>
       <c r="H4" t="str">
-        <v>460.1×320.1×3</v>
+        <v>410×370×0</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -547,22 +547,22 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C5" t="str">
-        <v>norm_case_1789766302590_63</v>
+        <v>norm_case_1789766302590_60</v>
       </c>
       <c r="D5" t="str">
-        <v>HINGE BRACKET</v>
+        <v>SPACER COLLAR</v>
       </c>
       <c r="E5" t="str">
-        <v>SS400</v>
+        <v>S45C</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.468</v>
+        <v>10.212</v>
       </c>
       <c r="H5" t="str">
-        <v>460.1×320.1×3</v>
+        <v>460.1×320.1×0</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -579,22 +579,22 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C6" t="str">
-        <v>norm_case_1789766302590_64</v>
+        <v>norm_case_1789766302590_61</v>
       </c>
       <c r="D6" t="str">
-        <v>STOPPER</v>
+        <v>HINGE SHAFT</v>
       </c>
       <c r="E6" t="str">
-        <v>SS400</v>
+        <v>S45C</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>3.468</v>
+        <v>10.212</v>
       </c>
       <c r="H6" t="str">
-        <v>460.1×320.1×3</v>
+        <v>460.1×320.1×0</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -611,22 +611,22 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C7" t="str">
-        <v>norm_case_1789766302590_65</v>
+        <v>norm_case_1789766302590_69</v>
       </c>
       <c r="D7" t="str">
-        <v>STOPPER</v>
+        <v>LOCKING PIN</v>
       </c>
       <c r="E7" t="str">
-        <v>SS400</v>
+        <v>S45C</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>3.468</v>
+        <v>10.212</v>
       </c>
       <c r="H7" t="str">
-        <v>460.1×320.1×3</v>
+        <v>460.1×320.1×0</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -643,22 +643,22 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C8" t="str">
-        <v>norm_case_1789766302590_69</v>
+        <v>norm_case_1789766302590_73</v>
       </c>
       <c r="D8" t="str">
-        <v>LOCKING PIN</v>
+        <v>ROLLER POST</v>
       </c>
       <c r="E8" t="str">
-        <v>S45C</v>
+        <v>SS400</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>3.468</v>
+        <v>10.212</v>
       </c>
       <c r="H8" t="str">
-        <v>460.1×320.1×3</v>
+        <v>460.1×240×0</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -675,22 +675,22 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C9" t="str">
-        <v>norm_case_1789766302590_74</v>
+        <v>norm_case_1789766302590_48</v>
       </c>
       <c r="D9" t="str">
-        <v>STOPPER PAD</v>
+        <v>POST</v>
       </c>
       <c r="E9" t="str">
-        <v>SS400</v>
+        <v>AL6061</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>3.468</v>
+        <v>7.494</v>
       </c>
       <c r="H9" t="str">
-        <v>460.1×320.1×3</v>
+        <v>620×375×0</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -707,10 +707,10 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C10" t="str">
-        <v>norm_case_1789766302590_2</v>
+        <v>norm_case_1789766302590_46</v>
       </c>
       <c r="D10" t="str">
-        <v>MAIN CHAIN DRIVE-1</v>
+        <v>FREE ROLLER</v>
       </c>
       <c r="E10" t="str">
         <v>SS400</v>
@@ -719,10 +719,10 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>2.61</v>
+        <v>4.834</v>
       </c>
       <c r="H10" t="str">
-        <v>367×302×3</v>
+        <v>424×400×0</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -739,10 +739,10 @@
         <v>가공품(MACHINING)</v>
       </c>
       <c r="C11" t="str">
-        <v>norm_case_1789766302590_72</v>
+        <v>norm_case_1789766302590_81</v>
       </c>
       <c r="D11" t="str">
-        <v>ROLLER POST</v>
+        <v>PIN TYPE GATE CONVEYOR</v>
       </c>
       <c r="E11" t="str">
         <v>AL6061</v>
@@ -751,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>2.6</v>
+        <v>4.587</v>
       </c>
       <c r="H11" t="str">
-        <v>460.1×240×3</v>
+        <v>150.2×120×0</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -771,22 +771,22 @@
         <v>판금품(SHEET_METAL)</v>
       </c>
       <c r="C12" t="str">
-        <v>norm_case_1789766302590_89</v>
+        <v>norm_case_1789766302590_47</v>
       </c>
       <c r="D12" t="str">
-        <v>MAIN C/V DRIVE COVER</v>
+        <v>BASE PLATE</v>
       </c>
       <c r="E12" t="str">
-        <v>SS400</v>
+        <v>AL6061</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>4.11</v>
+        <v>7.784</v>
       </c>
       <c r="H12" t="str">
-        <v>432×404×3</v>
+        <v>620×310×15</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -803,22 +803,22 @@
         <v>판금품(SHEET_METAL)</v>
       </c>
       <c r="C13" t="str">
-        <v>norm_case_1789766302590_90</v>
+        <v>norm_case_1789766302590_92</v>
       </c>
       <c r="D13" t="str">
-        <v>MAIN C/V DRIVE END COVER</v>
+        <v>MOTOR BRACKET</v>
       </c>
       <c r="E13" t="str">
-        <v>SS400</v>
+        <v>AL6061</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>4.11</v>
+        <v>7.129</v>
       </c>
       <c r="H13" t="str">
-        <v>432×404×3</v>
+        <v>660.05×400.01×10</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -835,10 +835,10 @@
         <v>판금품(SHEET_METAL)</v>
       </c>
       <c r="C14" t="str">
-        <v>norm_case_1789766302590_91</v>
+        <v>norm_case_1789766302590_50</v>
       </c>
       <c r="D14" t="str">
-        <v>MAIN C/V RETURN END COVER</v>
+        <v>SENSOR BRACKET</v>
       </c>
       <c r="E14" t="str">
         <v>SS400</v>
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>4.11</v>
+        <v>5.475</v>
       </c>
       <c r="H14" t="str">
-        <v>432×404×3</v>
+        <v>620×375×3</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -867,10 +867,10 @@
         <v>판금품(SHEET_METAL)</v>
       </c>
       <c r="C15" t="str">
-        <v>norm_case_1789766302590_98</v>
+        <v>norm_case_1789766302590_51</v>
       </c>
       <c r="D15" t="str">
-        <v>MAIN C/V RETURN END COVER</v>
+        <v>CONTROLLER BRACKET</v>
       </c>
       <c r="E15" t="str">
         <v>SS400</v>
@@ -879,10 +879,10 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>4.11</v>
+        <v>5.475</v>
       </c>
       <c r="H15" t="str">
-        <v>432×404×3</v>
+        <v>620×375×3</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -899,10 +899,10 @@
         <v>판금품(SHEET_METAL)</v>
       </c>
       <c r="C16" t="str">
-        <v>norm_case_1789766302590_99</v>
+        <v>norm_case_1789766302590_54</v>
       </c>
       <c r="D16" t="str">
-        <v>SUB C/V SHAFT COVER</v>
+        <v>GUIDE SHAFT</v>
       </c>
       <c r="E16" t="str">
         <v>SS400</v>
@@ -911,10 +911,10 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>3.032</v>
+        <v>5.475</v>
       </c>
       <c r="H16" t="str">
-        <v>432×298×3</v>
+        <v>620×375×3</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -931,10 +931,10 @@
         <v>판금품(SHEET_METAL)</v>
       </c>
       <c r="C17" t="str">
-        <v>norm_case_1789766302590_100</v>
+        <v>norm_case_1789766302590_54</v>
       </c>
       <c r="D17" t="str">
-        <v>SUB C/V SHAFT COVER</v>
+        <v>GUIDE SHAFT</v>
       </c>
       <c r="E17" t="str">
         <v>SS400</v>
@@ -943,10 +943,10 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>3.032</v>
+        <v>5.475</v>
       </c>
       <c r="H17" t="str">
-        <v>432×298×3</v>
+        <v>620×375×3</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -963,10 +963,10 @@
         <v>판금품(SHEET_METAL)</v>
       </c>
       <c r="C18" t="str">
-        <v>norm_case_1789766302590_101</v>
+        <v>norm_case_1789766302590_40</v>
       </c>
       <c r="D18" t="str">
-        <v>SUB C/V RETURN END COVER</v>
+        <v>STAY-BAR-2</v>
       </c>
       <c r="E18" t="str">
         <v>SS400</v>
@@ -975,10 +975,10 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>3.032</v>
+        <v>5.475</v>
       </c>
       <c r="H18" t="str">
-        <v>432×298×3</v>
+        <v>620×375×3</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -995,16 +995,16 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C19" t="str">
-        <v>norm_case_1789766302590_102</v>
+        <v>norm_case_1789766302590_3</v>
       </c>
       <c r="D19" t="str">
-        <v>10U+00B0</v>
+        <v>MOTOR BRACKET</v>
       </c>
       <c r="E19" t="str">
-        <v>-</v>
+        <v>1/</v>
       </c>
       <c r="F19">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G19" t="str">
         <v>-</v>
@@ -1027,13 +1027,13 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C20" t="str">
-        <v>norm_case_1789766302590_117</v>
+        <v>norm_case_1789766302590_4</v>
       </c>
       <c r="D20" t="str">
-        <v>2.P/N</v>
+        <v>MOTOR SHAFT</v>
       </c>
       <c r="E20" t="str">
-        <v>1.DIR</v>
+        <v>1/</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1059,13 +1059,13 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C21" t="str">
-        <v>norm_case_1789766302590_119</v>
+        <v>norm_case_1789766302590_5</v>
       </c>
       <c r="D21" t="str">
-        <v>MISUMI</v>
+        <v>SUB SHAFT</v>
       </c>
       <c r="E21" t="str">
-        <v>-</v>
+        <v>1/</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1091,13 +1091,13 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C22" t="str">
-        <v>norm_case_1789766302590_120</v>
+        <v>norm_case_1789766302590_6</v>
       </c>
       <c r="D22" t="str">
-        <v>ITOH</v>
+        <v>SUB SHAFT</v>
       </c>
       <c r="E22" t="str">
-        <v>ITOH</v>
+        <v>1/</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1123,16 +1123,16 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C23" t="str">
-        <v>norm_case_1789766302590_121</v>
+        <v>norm_case_1789766302590_7</v>
       </c>
       <c r="D23" t="str">
-        <v>CDQ2B63-25DMZ-A93L</v>
+        <v>MOTOR END CAP</v>
       </c>
       <c r="E23" t="str">
-        <v>-</v>
+        <v>1/</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="str">
         <v>-</v>
@@ -1155,13 +1155,13 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C24" t="str">
-        <v>norm_case_1789766302590_122</v>
+        <v>norm_case_1789766302590_9</v>
       </c>
       <c r="D24" t="str">
-        <v>FLOATING JOINT</v>
+        <v>MOTOR SHAFT</v>
       </c>
       <c r="E24" t="str">
-        <v>-</v>
+        <v>1/</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1187,13 +1187,13 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C25" t="str">
-        <v>norm_case_1789766302590_123</v>
+        <v>norm_case_1789766302590_10</v>
       </c>
       <c r="D25" t="str">
-        <v>LMF16UU</v>
+        <v>SUB SHAFT</v>
       </c>
       <c r="E25" t="str">
-        <v>-</v>
+        <v>1/</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1219,16 +1219,16 @@
         <v>구매품(PURCHASE)</v>
       </c>
       <c r="C26" t="str">
-        <v>norm_case_1789766302590_124</v>
+        <v>norm_case_1789766302590_11</v>
       </c>
       <c r="D26" t="str">
-        <v>열처리 HrC 45~55</v>
+        <v>SUB SHAFT</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>1/</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G26" t="str">
         <v>-</v>
